--- a/02_Literature_Review/Literature Matrix.xlsx
+++ b/02_Literature_Review/Literature Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishty\OneDrive\Desktop\MTech_Dissertation\02_Literature_Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB055821-E0A4-4EEA-BBD3-4F2A69C0F2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2B74D9-76DB-4B81-866D-5D9FEC12A65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{39A33124-AAD0-4B47-85EF-193804642DEE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Paper ID</t>
   </si>
@@ -84,6 +84,66 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Google SRE Book</t>
+  </si>
+  <si>
+    <t>F02</t>
+  </si>
+  <si>
+    <t>Google SRE Workbook</t>
+  </si>
+  <si>
+    <t>F03</t>
+  </si>
+  <si>
+    <t>Microsoft Learn – AKS Overview</t>
+  </si>
+  <si>
+    <t>F04</t>
+  </si>
+  <si>
+    <t>Microsoft Learn – Azure Monitor</t>
+  </si>
+  <si>
+    <t>F05</t>
+  </si>
+  <si>
+    <t>Microsoft Learn – Container Insights</t>
+  </si>
+  <si>
+    <t>F06</t>
+  </si>
+  <si>
+    <t>Kubernetes Documentation – Concepts</t>
+  </si>
+  <si>
+    <t>F07</t>
+  </si>
+  <si>
+    <t>Kubernetes Documentation – Deployments</t>
+  </si>
+  <si>
+    <t>F08</t>
+  </si>
+  <si>
+    <t>Kubernetes Documentation – Services</t>
+  </si>
+  <si>
+    <t>F09</t>
+  </si>
+  <si>
+    <t>CNCF – Kubernetes Production Best Practices</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>CNCF – Observability Whitepaper</t>
+  </si>
+  <si>
+    <t>F01</t>
   </si>
 </sst>
 </file>
@@ -127,54 +187,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <b/>
@@ -474,11 +499,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E66A90C8-95DB-4BDF-A7C6-A3DBE705AA1A}" name="Table1" displayName="Table1" ref="A1:O2" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:O2" xr:uid="{E66A90C8-95DB-4BDF-A7C6-A3DBE705AA1A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E66A90C8-95DB-4BDF-A7C6-A3DBE705AA1A}" name="Table1" displayName="Table1" ref="A1:O11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:O11" xr:uid="{E66A90C8-95DB-4BDF-A7C6-A3DBE705AA1A}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{D13704FB-1EA2-47BD-A6F4-9542370E5410}" name="Paper ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{49757138-10E1-45CE-B4B2-91DB76947CF2}" name="Title" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{D13704FB-1EA2-47BD-A6F4-9542370E5410}" name="Paper ID"/>
+    <tableColumn id="2" xr3:uid="{49757138-10E1-45CE-B4B2-91DB76947CF2}" name="Title"/>
     <tableColumn id="3" xr3:uid="{CAD0F298-10DF-4CDF-82E8-96BB4697873B}" name="Authors" dataDxfId="14"/>
     <tableColumn id="4" xr3:uid="{1122EA19-97CD-422D-8084-156B6CC30AAD}" name="Year" dataDxfId="13"/>
     <tableColumn id="5" xr3:uid="{B048CD19-1E1C-417D-AE1B-C48BFEDD5FA3}" name="Source" dataDxfId="12"/>
@@ -814,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4712BD8D-5C4A-433C-AED5-B06EEC5A7D26}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="11.28515625" customWidth="1"/>
@@ -868,9 +893,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -885,6 +914,195 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
+    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
